--- a/www/terminologies/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/www/terminologies/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:36:40+00:00</t>
+    <t>2026-08-27T16:10:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/www/terminologies/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T16:10:25+00:00</t>
+    <t>2026-09-28T13:22:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
